--- a/diseases/d157/2020-2025.xlsx
+++ b/diseases/d157/2020-2025.xlsx
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24198,7 +24198,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25770,7 +25770,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26556,7 +26556,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27342,7 +27342,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28128,7 +28128,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29700,7 +29700,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30879,7 +30879,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31665,7 +31665,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32451,7 +32451,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33237,7 +33237,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34023,7 +34023,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34809,7 +34809,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35595,7 +35595,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -36381,7 +36381,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37167,7 +37167,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37953,7 +37953,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39921,7 +39921,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -41103,7 +41103,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -42285,7 +42285,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -43467,7 +43467,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -44649,7 +44649,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -45831,7 +45831,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -47013,7 +47013,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -48195,7 +48195,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -49377,7 +49377,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -50559,7 +50559,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -51741,7 +51741,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -52923,7 +52923,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -54105,7 +54105,7 @@
       </c>
       <c r="AM273" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN273" t="b">
@@ -55287,7 +55287,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -56469,7 +56469,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -57651,7 +57651,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -58833,7 +58833,7 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -60015,7 +60015,7 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -61197,7 +61197,7 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -62379,7 +62379,7 @@
       </c>
       <c r="AM315" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN315" t="b">
@@ -63561,7 +63561,7 @@
       </c>
       <c r="AM321" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN321" t="b">
@@ -64743,7 +64743,7 @@
       </c>
       <c r="AM327" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN327" t="b">
@@ -65925,7 +65925,7 @@
       </c>
       <c r="AM333" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN333" t="b">
@@ -67107,7 +67107,7 @@
       </c>
       <c r="AM339" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN339" t="b">
@@ -68289,7 +68289,7 @@
       </c>
       <c r="AM345" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN345" t="b">

--- a/diseases/d157/2020-2025.xlsx
+++ b/diseases/d157/2020-2025.xlsx
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24198,7 +24198,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25770,7 +25770,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26556,7 +26556,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27342,7 +27342,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28128,7 +28128,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29700,7 +29700,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30879,7 +30879,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31665,7 +31665,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32451,7 +32451,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33237,7 +33237,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34023,7 +34023,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34809,7 +34809,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35595,7 +35595,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -36381,7 +36381,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37167,7 +37167,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37953,7 +37953,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39921,7 +39921,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -41103,7 +41103,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -42285,7 +42285,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -43467,7 +43467,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -44649,7 +44649,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -45831,7 +45831,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -47013,7 +47013,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -48195,7 +48195,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -49377,7 +49377,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -50559,7 +50559,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -51741,7 +51741,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -52923,7 +52923,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -54105,7 +54105,7 @@
       </c>
       <c r="AM273" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN273" t="b">
@@ -55287,7 +55287,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -56469,7 +56469,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -57651,7 +57651,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -58833,7 +58833,7 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -60015,7 +60015,7 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -61197,7 +61197,7 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -62379,7 +62379,7 @@
       </c>
       <c r="AM315" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN315" t="b">
@@ -63561,7 +63561,7 @@
       </c>
       <c r="AM321" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN321" t="b">
@@ -64743,7 +64743,7 @@
       </c>
       <c r="AM327" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN327" t="b">
@@ -65925,7 +65925,7 @@
       </c>
       <c r="AM333" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN333" t="b">
@@ -67107,7 +67107,7 @@
       </c>
       <c r="AM339" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN339" t="b">
@@ -68289,7 +68289,7 @@
       </c>
       <c r="AM345" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN345" t="b">

--- a/diseases/d157/2020-2025.xlsx
+++ b/diseases/d157/2020-2025.xlsx
@@ -62917,13 +62917,13 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O318" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R318" t="n">
-        <v>0.5724134442839497</v>
+        <v>0.5630296173284751</v>
       </c>
       <c r="S318" t="inlineStr">
         <is>
@@ -63076,10 +63076,10 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O319" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="U319" t="inlineStr">
         <is>
@@ -65281,13 +65281,13 @@
         </is>
       </c>
       <c r="N330" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O330" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R330" t="n">
-        <v>0.3472015973525597</v>
+        <v>0.337817770397085</v>
       </c>
       <c r="S330" t="inlineStr">
         <is>
@@ -65440,10 +65440,10 @@
         </is>
       </c>
       <c r="N331" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O331" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U331" t="inlineStr">
         <is>
@@ -69331,7 +69331,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18926</v>
+        <v>18924</v>
       </c>
     </row>
     <row r="16">
